--- a/aq_files/0740.xlsx
+++ b/aq_files/0740.xlsx
@@ -2,12 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +16,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -34,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,15 +49,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,860 +438,447 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Option B</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Details</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dropna() removes:</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Missing data</t>
+          <t>Arguments are:</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Values</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Columns</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) Passed values B) Function names C) Variables D) None</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fillna() replaces:</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Missing data</t>
+          <t>Parameters are:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Values</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Columns</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) Function variables B) Values C) Output D) None</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>groupby() used for:</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grouping</t>
+          <t>Default parameters allow:</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sorting</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Deleting</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) Optional args B) Mandatory C) None D) Loop</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sort_values():</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Keyword arguments use:</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Delete</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) name=value B) value only C) none D) random</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>merge() used for:</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Join tables</t>
+          <t>*args represents:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) multiple args B) one arg C) none D) list</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>concat() used for:</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Write function with default parameter.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>apply() applies:</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Function</t>
+          <t>Write function using keyword arguments.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>map() used for:</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Write function using *args to sum numbers.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sorting</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deleting</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>filter():</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Select data</t>
+          <t>Write function using **kwargs.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>duplicated():</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Find duplicates</t>
+          <t>Write function to swap values.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Unique</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>drop_duplicates():</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Remove duplicates</t>
+          <t>Write function to calculate average of numbers.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pivot():</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reshape</t>
+          <t>Write function to accept list and return max.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>aggregation means:</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Combine</t>
+          <t>Write function to accept string and return length.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Delete</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>transform():</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Modify data</t>
+          <t>Write function to return even numbers from list.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Define groupby.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Grouping operation</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>One Word</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Write function to multiply all elements.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LeetCode-style / logic-based</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Define merge.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Join datasets</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>One Word</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Write function to filter positive numbers.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LeetCode-style / logic-based</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Replace missing values with mean. Method?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>dropna</t>
+          <t>Write function to find min value.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fillna</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Join two tables on key column. Method?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>Write function to count occurrences.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>concat</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>groupby</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Apply custom function to column. Method?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>apply</t>
+          <t>Write function to return unique elements.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Remove duplicate records. Method?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>duplicated</t>
+          <t>Write function to find sum of list.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>drop_duplicates</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>groupby</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>